--- a/Supplementary_Table_S1.xlsx
+++ b/Supplementary_Table_S1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mavsuta-my.sharepoint.com/personal/jpdemuth_uta_edu/Documents/01 Research/2025 Behavior Ecology and Sociobiology/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mavsuta-my.sharepoint.com/personal/jpdemuth_uta_edu/Documents/GitHub/2026_hangry/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{594D9195-1481-A941-B7E3-57B4EAF479DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C879843-139D-8B40-9488-685656DA358E}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{8388E4AD-5245-AC41-8579-7C663DB2EF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{324D3CD5-3F98-1D4A-A0CC-2E6BCF881C69}"/>
   <bookViews>
     <workbookView xWindow="25360" yWindow="3600" windowWidth="29960" windowHeight="26360" xr2:uid="{290984DC-A909-FD4D-B2DB-F5845F80D1CE}"/>
   </bookViews>
@@ -2258,10 +2258,6 @@
     <row r="80" spans="1:5">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
-      <c r="C80" s="1">
-        <f>SUM(C2:C79)</f>
-        <v>2800</v>
-      </c>
       <c r="D80" s="1"/>
       <c r="E80" s="3"/>
     </row>
